--- a/Hardware/Controller/JLC_PCBA_CPL-DALI_EVG_Controller(V0.3).xlsx
+++ b/Hardware/Controller/JLC_PCBA_CPL-DALI_EVG_Controller(V0.3).xlsx
@@ -243,7 +243,7 @@
     <t>Bottom</t>
   </si>
   <si>
-    <t>220uF/50V</t>
+    <t>220uF/35V</t>
   </si>
   <si>
     <t>CAPR-5mm</t>
